--- a/hasil/2023_01_lipa_2.xlsx
+++ b/hasil/2023_01_lipa_2.xlsx
@@ -167,7 +167,7 @@
     <t>Mengetahui</t>
   </si>
   <si>
-    <t>Ternate , 31 Januari 2023</t>
+    <t>Ternate , 08 Maret 2023</t>
   </si>
   <si>
     <t xml:space="preserve">Ketua Pengadilan Agama Ternate </t>
